--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,684 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131659215</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493552</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7008261</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131660090</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493405</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7008198</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131660528</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7008296</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131661213</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästdrolkällan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493679</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7008328</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131659413</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493548</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7008257</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131659368</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493552</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7008261</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R4" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R5" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,12 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131661213</v>
+        <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1140,29 +1140,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493679</v>
+        <v>493524</v>
       </c>
       <c r="R6" t="n">
-        <v>7008328</v>
+        <v>7008296</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661213</v>
+        <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,46 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493679</v>
+        <v>493405</v>
       </c>
       <c r="R4" t="n">
-        <v>7008328</v>
+        <v>7008198</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,37 +1007,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R5" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R4" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131661213</v>
+        <v>131660528</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1016,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,29 +1033,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493679</v>
+        <v>493524</v>
       </c>
       <c r="R5" t="n">
-        <v>7008328</v>
+        <v>7008296</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1089,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,38 +1132,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R6" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,12 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661213</v>
+        <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,46 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493679</v>
+        <v>493405</v>
       </c>
       <c r="R4" t="n">
-        <v>7008328</v>
+        <v>7008198</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660528</v>
+        <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,24 +1024,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493524</v>
+        <v>493679</v>
       </c>
       <c r="R5" t="n">
-        <v>7008296</v>
+        <v>7008328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,12 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660090</v>
+        <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,34 +1123,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493405</v>
+        <v>493524</v>
       </c>
       <c r="R6" t="n">
-        <v>7008198</v>
+        <v>7008296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131661213</v>
+        <v>131660528</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,29 +1024,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493679</v>
+        <v>493524</v>
       </c>
       <c r="R5" t="n">
-        <v>7008328</v>
+        <v>7008296</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1080,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660528</v>
+        <v>131661213</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1140,24 +1140,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493524</v>
+        <v>493679</v>
       </c>
       <c r="R6" t="n">
-        <v>7008296</v>
+        <v>7008328</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,12 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660090</v>
+        <v>131660528</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493405</v>
+        <v>493524</v>
       </c>
       <c r="R4" t="n">
-        <v>7008198</v>
+        <v>7008296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +973,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660528</v>
+        <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1016,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,24 +1033,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493524</v>
+        <v>493679</v>
       </c>
       <c r="R5" t="n">
-        <v>7008296</v>
+        <v>7008328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,12 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131661213</v>
+        <v>131660090</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,46 +1132,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493679</v>
+        <v>493405</v>
       </c>
       <c r="R6" t="n">
-        <v>7008328</v>
+        <v>7008198</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,38 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R4" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +999,7 @@
         <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660090</v>
+        <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,34 +1123,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493405</v>
+        <v>493524</v>
       </c>
       <c r="R6" t="n">
-        <v>7008198</v>
+        <v>7008296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R4" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131661213</v>
+        <v>131660090</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,46 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493679</v>
+        <v>493405</v>
       </c>
       <c r="R5" t="n">
-        <v>7008328</v>
+        <v>7008198</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661213</v>
+        <v>131660528</v>
       </c>
       <c r="B4" t="n">
-        <v>57909</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,29 +917,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493679</v>
+        <v>493524</v>
       </c>
       <c r="R4" t="n">
-        <v>7008328</v>
+        <v>7008296</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +973,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,37 +1016,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R5" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B6" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,38 +1132,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R6" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,12 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131659953</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131659215</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,38 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R4" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +999,7 @@
         <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131660090</v>
+        <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,34 +1123,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493405</v>
+        <v>493524</v>
       </c>
       <c r="R6" t="n">
-        <v>7008198</v>
+        <v>7008296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
         <v>131659413</v>
       </c>
       <c r="B7" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131659368</v>
       </c>
       <c r="B8" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131659953</v>
+        <v>131659215</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493427</v>
+        <v>493552</v>
       </c>
       <c r="R2" t="n">
-        <v>7008182</v>
+        <v>7008261</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131659215</v>
+        <v>131659953</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493552</v>
+        <v>493427</v>
       </c>
       <c r="R3" t="n">
-        <v>7008261</v>
+        <v>7008182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131660528</v>
+        <v>131660090</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493524</v>
+        <v>493405</v>
       </c>
       <c r="R4" t="n">
-        <v>7008296</v>
+        <v>7008198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,48 +996,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131660090</v>
+        <v>131661213</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493405</v>
+        <v>493679</v>
       </c>
       <c r="R5" t="n">
-        <v>7008198</v>
+        <v>7008328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131661213</v>
+        <v>131660528</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1140,29 +1140,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Jmt</t>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493679</v>
+        <v>493524</v>
       </c>
       <c r="R6" t="n">
-        <v>7008328</v>
+        <v>7008296</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131659413</v>
+        <v>119731293</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>43249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,43 +1239,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>101248</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bringåsflon, Bringåsflon, Jmt</t>
+          <t>Bringåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493548</v>
+        <v>493606</v>
       </c>
       <c r="R7" t="n">
-        <v>7008257</v>
+        <v>7008384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,22 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1317,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131659368</v>
+        <v>117725353</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>43309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,43 +1340,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>201146</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+          <t>Bringåsflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493552</v>
+        <v>493713</v>
       </c>
       <c r="R8" t="n">
-        <v>7008261</v>
+        <v>7008370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,22 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,21 +1423,254 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131659368</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästdrolkällan, Hästdrolkällan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493552</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7008261</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Anne Siivola</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Anne Siivola</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131659413</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bringåsflon, Bringåsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493548</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7008257</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7439-2026 artfynd.xlsx
+++ b/artfynd/A 7439-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131659215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131659953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131660090</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131660528</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119731293</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117725353</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131659368</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,8 +1716,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131659413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>